--- a/docs/09-Project_Plan/9-Project_Plan.xlsx
+++ b/docs/09-Project_Plan/9-Project_Plan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\College_Backup\BTech_Internship\Persistent_Project\Dataset-Pipeline\NoCodeDatasetPreprocessing\docs\09-Project_Plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C79A6D55-FB8F-4F41-A88A-5F4023A74E10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD44B2C1-776E-4FB7-9405-AF75DD343E36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Documents" sheetId="3" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="273">
   <si>
     <t>Milestone Name</t>
   </si>
@@ -741,13 +741,146 @@
   </si>
   <si>
     <t>Data Analysis Draft</t>
+  </si>
+  <si>
+    <t>Comments</t>
+  </si>
+  <si>
+    <t>Considered a Summary project. Ruled out the summary project due to limited scope</t>
+  </si>
+  <si>
+    <t>Performed comparative analysis between several data preprocessing platforms</t>
+  </si>
+  <si>
+    <t>Understood the use of the project in real world</t>
+  </si>
+  <si>
+    <t>Defined what can be done earlist as a MVP for the project</t>
+  </si>
+  <si>
+    <t>Discussed and narrowed down the target users and ruled out non-technical users</t>
+  </si>
+  <si>
+    <t>Several ideations over how the dataset in and out would work</t>
+  </si>
+  <si>
+    <t>Created a draft, had issues with title and future scope. Rewrote those sections</t>
+  </si>
+  <si>
+    <t>Tried several layouts for streamlit, finalized a drop down based GUI</t>
+  </si>
+  <si>
+    <t>Used streamlit in built functions to get a drag and drop UI</t>
+  </si>
+  <si>
+    <t>Built the initial UI with help of Chatgpt and streamlit documentations</t>
+  </si>
+  <si>
+    <t>Implemented small operations and tried them out on diabetes dataset</t>
+  </si>
+  <si>
+    <t>Modified the diabetes dataset to increase the impurity</t>
+  </si>
+  <si>
+    <t>Checked how good of an application this can be if it made out into the world</t>
+  </si>
+  <si>
+    <t>None To Demo</t>
+  </si>
+  <si>
+    <t>Note: Need to learn 2 new technologies for this milestone, so tentatively allocating 3 weeks. Also festive events are present which may unexpected alter the schedule</t>
+  </si>
+  <si>
+    <t>25/09/2026</t>
+  </si>
+  <si>
+    <t>28/09/2026</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Note: Testing may take a while longer, also college related contents will be present during this period. Allocating way more time here, but there exists a possiblity of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>early completion</t>
+    </r>
+  </si>
+  <si>
+    <t>16/10/2026</t>
+  </si>
+  <si>
+    <t>Remaining time (half october + 15 days of november) can be allocated to working on advance scope (future scope). The project's main scope will have already finished.</t>
+  </si>
+  <si>
+    <t>Experimented with a single file structure but ruled it out due to complexity</t>
+  </si>
+  <si>
+    <t>Implemented 1 dataframe session management as a modular session file</t>
+  </si>
+  <si>
+    <t>Summary failed a few times till the function was written to output onto streamlit</t>
+  </si>
+  <si>
+    <t>Finalized the modular approach since it can help to add and remove features later on</t>
+  </si>
+  <si>
+    <t>Made 3 basic operations to check if the platform works properly</t>
+  </si>
+  <si>
+    <t>Made sure that string data was made uniform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As per the project description CSV and XLSX are options, but realistically people would use CSV more </t>
+  </si>
+  <si>
+    <t>Implemented these as a part of extra preprocessing because not large enough to have a separate milestone</t>
+  </si>
+  <si>
+    <t>Broke the system to root components, very detailed at first but then abstracted</t>
+  </si>
+  <si>
+    <t>Created a basic UML diagram for clear real world use and how the users will use it</t>
+  </si>
+  <si>
+    <t>With help from AI, wrote several requirements analysis sections, required lot of rewriting and reworking to make it fit the project</t>
+  </si>
+  <si>
+    <t>With help from AI found out how to abstract the system to high level architecture</t>
+  </si>
+  <si>
+    <t>With help from AI wrote some acceptance scenarios for the use cases, took lot of rewriting</t>
+  </si>
+  <si>
+    <t>Cleaned up the textual contents of code for each module to make it easy to read</t>
+  </si>
+  <si>
+    <t>Settled for 2 encoding methods instead of every single method, this will help to keep testing in bounds</t>
+  </si>
+  <si>
+    <t>Settled for 2 scaling methods instead of just 1 minmax, having option of 2 helps to target specific columns better</t>
+  </si>
+  <si>
+    <t>As most data needs to be normalized, standardscaler was a good idea instead of manually writing maths code</t>
+  </si>
+  <si>
+    <t>Researching how heatmaps can be displayed properly on streamlit</t>
+  </si>
+  <si>
+    <t>Added an extra section, which I later got to know, I should not be doing as this expands the scope, should have added this in the initial draft itself</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -787,6 +920,14 @@
     <font>
       <sz val="11"/>
       <color theme="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -833,7 +974,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -875,6 +1016,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1369,7 +1513,7 @@
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -1378,13 +1522,14 @@
     <col min="4" max="4" width="10.7109375" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15" style="2" customWidth="1"/>
-    <col min="7" max="7" width="10.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="2"/>
+    <col min="10" max="10" width="73.28515625" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
@@ -1413,7 +1558,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>17</v>
       </c>
@@ -1433,7 +1578,7 @@
         <v>94</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>97</v>
+        <v>247</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>19</v>
@@ -1442,7 +1587,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>18</v>
       </c>
@@ -1462,7 +1607,7 @@
         <v>88</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>97</v>
+        <v>247</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>19</v>
@@ -1471,7 +1616,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>20</v>
       </c>
@@ -1500,7 +1645,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>22</v>
       </c>
@@ -1529,7 +1674,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>24</v>
       </c>
@@ -1548,17 +1693,17 @@
       <c r="F6" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>96</v>
+      <c r="G6" s="7">
+        <v>46121</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>162</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>25</v>
       </c>
@@ -1568,11 +1713,11 @@
       <c r="C7" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>215</v>
+      <c r="D7" s="7">
+        <v>46212</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>215</v>
+        <v>249</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>215</v>
@@ -1584,10 +1729,13 @@
         <v>21</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>26</v>
       </c>
@@ -1598,10 +1746,10 @@
         <v>57</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>215</v>
+        <v>250</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>215</v>
+        <v>252</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>215</v>
@@ -1613,10 +1761,13 @@
         <v>21</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="J8" s="12" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>30</v>
       </c>
@@ -1642,7 +1793,10 @@
         <v>32</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>215</v>
+        <v>21</v>
+      </c>
+      <c r="J9" s="12" t="s">
+        <v>253</v>
       </c>
     </row>
   </sheetData>
@@ -1655,7 +1809,7 @@
   <sheetPr>
     <tabColor theme="5" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="2" bestFit="1" customWidth="1"/>
@@ -1665,14 +1819,14 @@
     <col min="5" max="5" width="11.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="22.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="35.7109375" style="6" customWidth="1"/>
-    <col min="9" max="9" width="12.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="2"/>
+    <col min="8" max="9" width="35.7109375" style="6" customWidth="1"/>
+    <col min="10" max="10" width="12.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
         <v>27</v>
       </c>
@@ -1686,8 +1840,9 @@
       <c r="I1" s="14"/>
       <c r="J1" s="14"/>
       <c r="K1" s="14"/>
-    </row>
-    <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L1" s="14"/>
+    </row>
+    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -1712,17 +1867,20 @@
       <c r="H2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="J2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>34</v>
       </c>
@@ -1747,8 +1905,8 @@
       <c r="H3" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="I3" s="3" t="s">
-        <v>96</v>
+      <c r="I3" s="5" t="s">
+        <v>234</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>96</v>
@@ -1756,8 +1914,11 @@
       <c r="K3" s="3" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="L3" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>42</v>
       </c>
@@ -1782,8 +1943,8 @@
       <c r="H4" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="I4" s="3" t="s">
-        <v>96</v>
+      <c r="I4" s="5" t="s">
+        <v>234</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>96</v>
@@ -1791,8 +1952,11 @@
       <c r="K4" s="3" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L4" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>43</v>
       </c>
@@ -1817,8 +1981,8 @@
       <c r="H5" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="I5" s="3" t="s">
-        <v>96</v>
+      <c r="I5" s="5" t="s">
+        <v>235</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>96</v>
@@ -1826,8 +1990,11 @@
       <c r="K5" s="3" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L5" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>44</v>
       </c>
@@ -1852,8 +2019,8 @@
       <c r="H6" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="I6" s="3" t="s">
-        <v>96</v>
+      <c r="I6" s="5" t="s">
+        <v>236</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>96</v>
@@ -1861,8 +2028,11 @@
       <c r="K6" s="3" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="L6" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>45</v>
       </c>
@@ -1887,8 +2057,8 @@
       <c r="H7" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="I7" s="3" t="s">
-        <v>96</v>
+      <c r="I7" s="5" t="s">
+        <v>237</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>96</v>
@@ -1896,8 +2066,11 @@
       <c r="K7" s="3" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="L7" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>46</v>
       </c>
@@ -1922,8 +2095,8 @@
       <c r="H8" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>96</v>
+      <c r="I8" s="5" t="s">
+        <v>238</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>96</v>
@@ -1931,8 +2104,11 @@
       <c r="K8" s="3" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="L8" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>47</v>
       </c>
@@ -1957,8 +2133,8 @@
       <c r="H9" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>96</v>
+      <c r="I9" s="5" t="s">
+        <v>239</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>96</v>
@@ -1966,8 +2142,11 @@
       <c r="K9" s="3" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L9" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>48</v>
       </c>
@@ -1992,19 +2171,22 @@
       <c r="H10" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>96</v>
+      <c r="I10" s="5" t="s">
+        <v>240</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>96</v>
       </c>
       <c r="K10" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="L10" s="3" t="s">
         <v>96</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A1:L1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2016,7 +2198,7 @@
   <sheetPr>
     <tabColor theme="5" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="2" bestFit="1" customWidth="1"/>
@@ -2026,14 +2208,14 @@
     <col min="5" max="5" width="11.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="22.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="35.7109375" style="6" customWidth="1"/>
-    <col min="9" max="9" width="12.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="2"/>
+    <col min="8" max="9" width="35.7109375" style="6" customWidth="1"/>
+    <col min="10" max="10" width="12.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
         <v>28</v>
       </c>
@@ -2047,8 +2229,9 @@
       <c r="I1" s="14"/>
       <c r="J1" s="14"/>
       <c r="K1" s="14"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L1" s="14"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -2073,17 +2256,20 @@
       <c r="H2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="J2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>111</v>
       </c>
@@ -2108,8 +2294,8 @@
       <c r="H3" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="I3" s="3" t="s">
-        <v>96</v>
+      <c r="I3" s="5" t="s">
+        <v>241</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>96</v>
@@ -2117,8 +2303,11 @@
       <c r="K3" s="3" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L3" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>112</v>
       </c>
@@ -2143,8 +2332,8 @@
       <c r="H4" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="I4" s="3" t="s">
-        <v>96</v>
+      <c r="I4" s="5" t="s">
+        <v>242</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>96</v>
@@ -2152,8 +2341,11 @@
       <c r="K4" s="3" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L4" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>113</v>
       </c>
@@ -2178,8 +2370,8 @@
       <c r="H5" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="I5" s="3" t="s">
-        <v>96</v>
+      <c r="I5" s="5" t="s">
+        <v>243</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>96</v>
@@ -2187,8 +2379,11 @@
       <c r="K5" s="3" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L5" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>114</v>
       </c>
@@ -2213,8 +2408,8 @@
       <c r="H6" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="I6" s="3" t="s">
-        <v>96</v>
+      <c r="I6" s="5" t="s">
+        <v>244</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>96</v>
@@ -2222,8 +2417,11 @@
       <c r="K6" s="3" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="L6" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>115</v>
       </c>
@@ -2248,8 +2446,8 @@
       <c r="H7" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="I7" s="3" t="s">
-        <v>96</v>
+      <c r="I7" s="5" t="s">
+        <v>245</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>96</v>
@@ -2257,8 +2455,11 @@
       <c r="K7" s="3" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="L7" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>116</v>
       </c>
@@ -2283,19 +2484,22 @@
       <c r="H8" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>96</v>
+      <c r="I8" s="5" t="s">
+        <v>246</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>96</v>
       </c>
       <c r="K8" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="L8" s="3" t="s">
         <v>96</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A1:L1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2307,7 +2511,7 @@
   <sheetPr>
     <tabColor theme="5" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="2" bestFit="1" customWidth="1"/>
@@ -2317,14 +2521,14 @@
     <col min="5" max="5" width="11.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="22.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="35.7109375" style="6" customWidth="1"/>
-    <col min="9" max="9" width="12.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="2"/>
+    <col min="8" max="9" width="35.7109375" style="6" customWidth="1"/>
+    <col min="10" max="10" width="12.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
         <v>54</v>
       </c>
@@ -2338,8 +2542,9 @@
       <c r="I1" s="14"/>
       <c r="J1" s="14"/>
       <c r="K1" s="14"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L1" s="14"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -2364,17 +2569,20 @@
       <c r="H2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="J2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>131</v>
       </c>
@@ -2399,8 +2607,8 @@
       <c r="H3" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="I3" s="3" t="s">
-        <v>96</v>
+      <c r="I3" s="5" t="s">
+        <v>254</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>96</v>
@@ -2408,8 +2616,11 @@
       <c r="K3" s="3" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L3" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>132</v>
       </c>
@@ -2434,8 +2645,8 @@
       <c r="H4" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="I4" s="3" t="s">
-        <v>96</v>
+      <c r="I4" s="5" t="s">
+        <v>255</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>96</v>
@@ -2443,8 +2654,11 @@
       <c r="K4" s="3" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="L4" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>133</v>
       </c>
@@ -2469,8 +2683,8 @@
       <c r="H5" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="I5" s="3" t="s">
-        <v>96</v>
+      <c r="I5" s="5" t="s">
+        <v>256</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>96</v>
@@ -2478,8 +2692,11 @@
       <c r="K5" s="3" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L5" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>134</v>
       </c>
@@ -2504,8 +2721,8 @@
       <c r="H6" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="I6" s="3" t="s">
-        <v>96</v>
+      <c r="I6" s="5" t="s">
+        <v>257</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>96</v>
@@ -2513,8 +2730,11 @@
       <c r="K6" s="3" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L6" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>135</v>
       </c>
@@ -2539,8 +2759,8 @@
       <c r="H7" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="I7" s="3" t="s">
-        <v>96</v>
+      <c r="I7" s="5" t="s">
+        <v>258</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>96</v>
@@ -2548,8 +2768,11 @@
       <c r="K7" s="3" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L7" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>136</v>
       </c>
@@ -2574,8 +2797,8 @@
       <c r="H8" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>96</v>
+      <c r="I8" s="5" t="s">
+        <v>259</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>96</v>
@@ -2583,8 +2806,11 @@
       <c r="K8" s="3" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L8" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>142</v>
       </c>
@@ -2609,8 +2835,8 @@
       <c r="H9" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>96</v>
+      <c r="I9" s="5" t="s">
+        <v>260</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>96</v>
@@ -2618,8 +2844,11 @@
       <c r="K9" s="3" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L9" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>154</v>
       </c>
@@ -2644,19 +2873,22 @@
       <c r="H10" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>96</v>
+      <c r="I10" s="5" t="s">
+        <v>261</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>96</v>
       </c>
       <c r="K10" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="L10" s="3" t="s">
         <v>96</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A1:L1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2668,7 +2900,7 @@
   <sheetPr>
     <tabColor theme="5" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="2" bestFit="1" customWidth="1"/>
@@ -2678,14 +2910,14 @@
     <col min="5" max="5" width="11.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="22.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="35.7109375" style="6" customWidth="1"/>
-    <col min="9" max="9" width="12.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="2"/>
+    <col min="8" max="9" width="35.7109375" style="6" customWidth="1"/>
+    <col min="10" max="10" width="12.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
         <v>29</v>
       </c>
@@ -2699,8 +2931,9 @@
       <c r="I1" s="14"/>
       <c r="J1" s="14"/>
       <c r="K1" s="14"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L1" s="14"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -2725,17 +2958,20 @@
       <c r="H2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="J2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>172</v>
       </c>
@@ -2760,8 +2996,8 @@
       <c r="H3" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="I3" s="3" t="s">
-        <v>96</v>
+      <c r="I3" s="5" t="s">
+        <v>265</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>96</v>
@@ -2769,8 +3005,11 @@
       <c r="K3" s="3" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L3" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>173</v>
       </c>
@@ -2795,8 +3034,8 @@
       <c r="H4" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="I4" s="3" t="s">
-        <v>96</v>
+      <c r="I4" s="5" t="s">
+        <v>262</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>96</v>
@@ -2804,8 +3043,11 @@
       <c r="K4" s="3" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="L4" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>174</v>
       </c>
@@ -2830,8 +3072,8 @@
       <c r="H5" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="I5" s="3" t="s">
-        <v>96</v>
+      <c r="I5" s="5" t="s">
+        <v>266</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>96</v>
@@ -2839,8 +3081,11 @@
       <c r="K5" s="3" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L5" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>175</v>
       </c>
@@ -2865,7 +3110,7 @@
       <c r="H6" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="I6" s="5" t="s">
         <v>96</v>
       </c>
       <c r="J6" s="3" t="s">
@@ -2874,8 +3119,11 @@
       <c r="K6" s="3" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L6" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>176</v>
       </c>
@@ -2900,7 +3148,7 @@
       <c r="H7" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="I7" s="5" t="s">
         <v>96</v>
       </c>
       <c r="J7" s="3" t="s">
@@ -2909,8 +3157,11 @@
       <c r="K7" s="3" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L7" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>177</v>
       </c>
@@ -2935,7 +3186,7 @@
       <c r="H8" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="I8" s="5" t="s">
         <v>96</v>
       </c>
       <c r="J8" s="3" t="s">
@@ -2944,8 +3195,11 @@
       <c r="K8" s="3" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="L8" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>178</v>
       </c>
@@ -2970,8 +3224,8 @@
       <c r="H9" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>96</v>
+      <c r="I9" s="5" t="s">
+        <v>263</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>96</v>
@@ -2979,8 +3233,11 @@
       <c r="K9" s="3" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L9" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>179</v>
       </c>
@@ -3005,8 +3262,8 @@
       <c r="H10" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>96</v>
+      <c r="I10" s="5" t="s">
+        <v>264</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>96</v>
@@ -3014,8 +3271,11 @@
       <c r="K10" s="3" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L10" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>180</v>
       </c>
@@ -3040,7 +3300,7 @@
       <c r="H11" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="I11" s="3" t="s">
+      <c r="I11" s="5" t="s">
         <v>96</v>
       </c>
       <c r="J11" s="3" t="s">
@@ -3049,8 +3309,11 @@
       <c r="K11" s="3" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L11" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>181</v>
       </c>
@@ -3075,19 +3338,22 @@
       <c r="H12" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="I12" s="3" t="s">
+      <c r="I12" s="5" t="s">
         <v>96</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>96</v>
       </c>
       <c r="K12" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="L12" s="3" t="s">
         <v>96</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A1:L1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3099,7 +3365,7 @@
   <sheetPr>
     <tabColor theme="5" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="2" bestFit="1" customWidth="1"/>
@@ -3109,15 +3375,15 @@
     <col min="5" max="5" width="11.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="22.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="35.7109375" style="6" customWidth="1"/>
-    <col min="9" max="9" width="12.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="2"/>
+    <col min="8" max="9" width="35.7109375" style="6" customWidth="1"/>
+    <col min="10" max="10" width="12.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.85546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
         <v>55</v>
       </c>
@@ -3131,8 +3397,9 @@
       <c r="I1" s="14"/>
       <c r="J1" s="14"/>
       <c r="K1" s="14"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L1" s="14"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -3157,17 +3424,20 @@
       <c r="H2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="J2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>194</v>
       </c>
@@ -3192,8 +3462,8 @@
       <c r="H3" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="I3" s="3" t="s">
-        <v>96</v>
+      <c r="I3" s="5" t="s">
+        <v>267</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>96</v>
@@ -3201,8 +3471,11 @@
       <c r="K3" s="3" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L3" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>195</v>
       </c>
@@ -3227,8 +3500,8 @@
       <c r="H4" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="I4" s="3" t="s">
-        <v>96</v>
+      <c r="I4" s="5" t="s">
+        <v>268</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>96</v>
@@ -3236,8 +3509,11 @@
       <c r="K4" s="3" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L4" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>196</v>
       </c>
@@ -3262,8 +3538,8 @@
       <c r="H5" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="I5" s="3" t="s">
-        <v>96</v>
+      <c r="I5" s="5" t="s">
+        <v>269</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>96</v>
@@ -3271,8 +3547,11 @@
       <c r="K5" s="3" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L5" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>197</v>
       </c>
@@ -3297,8 +3576,8 @@
       <c r="H6" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="I6" s="3" t="s">
-        <v>96</v>
+      <c r="I6" s="5" t="s">
+        <v>270</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>96</v>
@@ -3306,8 +3585,11 @@
       <c r="K6" s="3" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="L6" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>198</v>
       </c>
@@ -3332,11 +3614,14 @@
       <c r="H7" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="I7" s="3"/>
+      <c r="I7" s="5" t="s">
+        <v>271</v>
+      </c>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
-    </row>
-    <row r="8" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="L7" s="3"/>
+    </row>
+    <row r="8" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>199</v>
       </c>
@@ -3361,8 +3646,8 @@
       <c r="H8" s="12" t="s">
         <v>223</v>
       </c>
-      <c r="I8" s="11" t="s">
-        <v>96</v>
+      <c r="I8" s="12" t="s">
+        <v>272</v>
       </c>
       <c r="J8" s="11" t="s">
         <v>96</v>
@@ -3370,11 +3655,14 @@
       <c r="K8" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="L8" s="6" t="s">
+      <c r="L8" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="M8" s="6" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>220</v>
       </c>
@@ -3399,19 +3687,22 @@
       <c r="H9" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="I9" s="5" t="s">
         <v>96</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>96</v>
       </c>
       <c r="K9" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="L9" s="3" t="s">
         <v>96</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A1:L1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/09-Project_Plan/9-Project_Plan.xlsx
+++ b/docs/09-Project_Plan/9-Project_Plan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\College_Backup\BTech_Internship\Persistent_Project\Dataset-Pipeline\NoCodeDatasetPreprocessing\docs\09-Project_Plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD44B2C1-776E-4FB7-9405-AF75DD343E36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE640BE0-634D-49AD-8BC0-E01F2B25E5E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Documents" sheetId="3" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="275">
   <si>
     <t>Milestone Name</t>
   </si>
@@ -870,10 +870,16 @@
     <t>As most data needs to be normalized, standardscaler was a good idea instead of manually writing maths code</t>
   </si>
   <si>
-    <t>Researching how heatmaps can be displayed properly on streamlit</t>
-  </si>
-  <si>
-    <t>Added an extra section, which I later got to know, I should not be doing as this expands the scope, should have added this in the initial draft itself</t>
+    <t>31/08/2026 (major)</t>
+  </si>
+  <si>
+    <t>Researching how heatmaps can be displayed properly on streamlit. Trial and error about how to render the image</t>
+  </si>
+  <si>
+    <t>31/08/2026 (half)</t>
+  </si>
+  <si>
+    <t>Added an extra section, which I later got to know, I should not be doing as this expands the scope, should have added this in the initial draft itself. Implemented basic info,pcc,null count</t>
   </si>
 </sst>
 </file>
@@ -1015,10 +1021,10 @@
     <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1827,20 +1833,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2216,20 +2222,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2256,7 +2262,7 @@
       <c r="H2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="15" t="s">
+      <c r="I2" s="14" t="s">
         <v>233</v>
       </c>
       <c r="J2" s="1" t="s">
@@ -2529,20 +2535,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2918,20 +2924,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -3384,20 +3390,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -3589,7 +3595,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>198</v>
       </c>
@@ -3609,19 +3615,19 @@
         <v>219</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>96</v>
+        <v>271</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>214</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
     </row>
-    <row r="8" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>199</v>
       </c>
@@ -3641,13 +3647,13 @@
         <v>219</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>96</v>
+        <v>273</v>
       </c>
       <c r="H8" s="12" t="s">
         <v>223</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="J8" s="11" t="s">
         <v>96</v>

--- a/docs/09-Project_Plan/9-Project_Plan.xlsx
+++ b/docs/09-Project_Plan/9-Project_Plan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\College_Backup\BTech_Internship\Persistent_Project\Dataset-Pipeline\NoCodeDatasetPreprocessing\docs\09-Project_Plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE640BE0-634D-49AD-8BC0-E01F2B25E5E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5CF564D-8AE0-4A54-AB06-77C8B3D869CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="317" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Documents" sheetId="3" r:id="rId1"/>
@@ -797,8 +797,98 @@
     <t>28/09/2026</t>
   </si>
   <si>
+    <t>16/10/2026</t>
+  </si>
+  <si>
+    <t>Remaining time (half october + 15 days of november) can be allocated to working on advance scope (future scope). The project's main scope will have already finished.</t>
+  </si>
+  <si>
+    <t>Experimented with a single file structure but ruled it out due to complexity</t>
+  </si>
+  <si>
+    <t>Implemented 1 dataframe session management as a modular session file</t>
+  </si>
+  <si>
+    <t>Summary failed a few times till the function was written to output onto streamlit</t>
+  </si>
+  <si>
+    <t>Finalized the modular approach since it can help to add and remove features later on</t>
+  </si>
+  <si>
+    <t>Made 3 basic operations to check if the platform works properly</t>
+  </si>
+  <si>
+    <t>Made sure that string data was made uniform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As per the project description CSV and XLSX are options, but realistically people would use CSV more </t>
+  </si>
+  <si>
+    <t>Implemented these as a part of extra preprocessing because not large enough to have a separate milestone</t>
+  </si>
+  <si>
+    <t>Broke the system to root components, very detailed at first but then abstracted</t>
+  </si>
+  <si>
+    <t>Created a basic UML diagram for clear real world use and how the users will use it</t>
+  </si>
+  <si>
+    <t>With help from AI, wrote several requirements analysis sections, required lot of rewriting and reworking to make it fit the project</t>
+  </si>
+  <si>
+    <t>With help from AI found out how to abstract the system to high level architecture</t>
+  </si>
+  <si>
+    <t>With help from AI wrote some acceptance scenarios for the use cases, took lot of rewriting</t>
+  </si>
+  <si>
+    <t>Cleaned up the textual contents of code for each module to make it easy to read</t>
+  </si>
+  <si>
+    <t>Settled for 2 encoding methods instead of every single method, this will help to keep testing in bounds</t>
+  </si>
+  <si>
+    <t>Settled for 2 scaling methods instead of just 1 minmax, having option of 2 helps to target specific columns better</t>
+  </si>
+  <si>
+    <t>As most data needs to be normalized, standardscaler was a good idea instead of manually writing maths code</t>
+  </si>
+  <si>
+    <t>31/08/2026 (major)</t>
+  </si>
+  <si>
+    <t>Researching how heatmaps can be displayed properly on streamlit. Trial and error about how to render the image</t>
+  </si>
+  <si>
+    <t>31/08/2026 (half)</t>
+  </si>
+  <si>
+    <t>Added an extra section, which I later got to know, I should not be doing as this expands the scope, should have added this in the initial draft itself. Implemented basic info,pcc,null count</t>
+  </si>
+  <si>
     <r>
-      <t xml:space="preserve">Note: Testing may take a while longer, also college related contents will be present during this period. Allocating way more time here, but there exists a possiblity of </t>
+      <t xml:space="preserve">Note: Testing may take a while longer, also college related contents will be present during this period. Allocating way more time here, but there exists a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>possiblity of</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
@@ -811,75 +901,6 @@
       </rPr>
       <t>early completion</t>
     </r>
-  </si>
-  <si>
-    <t>16/10/2026</t>
-  </si>
-  <si>
-    <t>Remaining time (half october + 15 days of november) can be allocated to working on advance scope (future scope). The project's main scope will have already finished.</t>
-  </si>
-  <si>
-    <t>Experimented with a single file structure but ruled it out due to complexity</t>
-  </si>
-  <si>
-    <t>Implemented 1 dataframe session management as a modular session file</t>
-  </si>
-  <si>
-    <t>Summary failed a few times till the function was written to output onto streamlit</t>
-  </si>
-  <si>
-    <t>Finalized the modular approach since it can help to add and remove features later on</t>
-  </si>
-  <si>
-    <t>Made 3 basic operations to check if the platform works properly</t>
-  </si>
-  <si>
-    <t>Made sure that string data was made uniform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As per the project description CSV and XLSX are options, but realistically people would use CSV more </t>
-  </si>
-  <si>
-    <t>Implemented these as a part of extra preprocessing because not large enough to have a separate milestone</t>
-  </si>
-  <si>
-    <t>Broke the system to root components, very detailed at first but then abstracted</t>
-  </si>
-  <si>
-    <t>Created a basic UML diagram for clear real world use and how the users will use it</t>
-  </si>
-  <si>
-    <t>With help from AI, wrote several requirements analysis sections, required lot of rewriting and reworking to make it fit the project</t>
-  </si>
-  <si>
-    <t>With help from AI found out how to abstract the system to high level architecture</t>
-  </si>
-  <si>
-    <t>With help from AI wrote some acceptance scenarios for the use cases, took lot of rewriting</t>
-  </si>
-  <si>
-    <t>Cleaned up the textual contents of code for each module to make it easy to read</t>
-  </si>
-  <si>
-    <t>Settled for 2 encoding methods instead of every single method, this will help to keep testing in bounds</t>
-  </si>
-  <si>
-    <t>Settled for 2 scaling methods instead of just 1 minmax, having option of 2 helps to target specific columns better</t>
-  </si>
-  <si>
-    <t>As most data needs to be normalized, standardscaler was a good idea instead of manually writing maths code</t>
-  </si>
-  <si>
-    <t>31/08/2026 (major)</t>
-  </si>
-  <si>
-    <t>Researching how heatmaps can be displayed properly on streamlit. Trial and error about how to render the image</t>
-  </si>
-  <si>
-    <t>31/08/2026 (half)</t>
-  </si>
-  <si>
-    <t>Added an extra section, which I later got to know, I should not be doing as this expands the scope, should have added this in the initial draft itself. Implemented basic info,pcc,null count</t>
   </si>
 </sst>
 </file>
@@ -1755,7 +1776,7 @@
         <v>250</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>215</v>
@@ -1770,7 +1791,7 @@
         <v>21</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>251</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="45" x14ac:dyDescent="0.25">
@@ -1802,7 +1823,7 @@
         <v>21</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
   </sheetData>
@@ -2614,7 +2635,7 @@
         <v>159</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>96</v>
@@ -2652,7 +2673,7 @@
         <v>160</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>96</v>
@@ -2690,7 +2711,7 @@
         <v>159</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>96</v>
@@ -2728,7 +2749,7 @@
         <v>159</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>96</v>
@@ -2766,7 +2787,7 @@
         <v>161</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>96</v>
@@ -2804,7 +2825,7 @@
         <v>161</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>96</v>
@@ -2842,7 +2863,7 @@
         <v>128</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>96</v>
@@ -2880,7 +2901,7 @@
         <v>159</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>96</v>
@@ -3003,7 +3024,7 @@
         <v>128</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>96</v>
@@ -3041,7 +3062,7 @@
         <v>71</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>96</v>
@@ -3079,7 +3100,7 @@
         <v>128</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>96</v>
@@ -3231,7 +3252,7 @@
         <v>71</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>96</v>
@@ -3269,7 +3290,7 @@
         <v>193</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>96</v>
@@ -3469,7 +3490,7 @@
         <v>97</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>96</v>
@@ -3507,7 +3528,7 @@
         <v>213</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>96</v>
@@ -3545,7 +3566,7 @@
         <v>213</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>96</v>
@@ -3583,7 +3604,7 @@
         <v>213</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>96</v>
@@ -3612,16 +3633,16 @@
         <v>46031</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>219</v>
+        <v>19</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>214</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
@@ -3647,13 +3668,13 @@
         <v>219</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H8" s="12" t="s">
         <v>223</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="J8" s="11" t="s">
         <v>96</v>

--- a/docs/09-Project_Plan/9-Project_Plan.xlsx
+++ b/docs/09-Project_Plan/9-Project_Plan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\College_Backup\BTech_Internship\Persistent_Project\Dataset-Pipeline\NoCodeDatasetPreprocessing\docs\09-Project_Plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5CF564D-8AE0-4A54-AB06-77C8B3D869CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71FE0C61-3DD5-42CA-8CCF-6020EB1F18F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="317" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="317" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Documents" sheetId="3" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="275">
   <si>
     <t>Milestone Name</t>
   </si>
@@ -701,9 +701,6 @@
     <t>Review</t>
   </si>
   <si>
-    <t>In progress</t>
-  </si>
-  <si>
     <t>M5T7</t>
   </si>
   <si>
@@ -858,9 +855,6 @@
   </si>
   <si>
     <t>Researching how heatmaps can be displayed properly on streamlit. Trial and error about how to render the image</t>
-  </si>
-  <si>
-    <t>31/08/2026 (half)</t>
   </si>
   <si>
     <t>Added an extra section, which I later got to know, I should not be doing as this expands the scope, should have added this in the initial draft itself. Implemented basic info,pcc,null count</t>
@@ -901,6 +895,12 @@
       </rPr>
       <t>early completion</t>
     </r>
+  </si>
+  <si>
+    <t>01/09/2026 (major)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Researched the best flow for linear preprocessing and made sure the modules are structured like that </t>
   </si>
 </sst>
 </file>
@@ -1480,10 +1480,10 @@
         <v>85</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>229</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>230</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>67</v>
@@ -1497,10 +1497,10 @@
         <v>212</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>231</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>232</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>72</v>
@@ -1605,7 +1605,7 @@
         <v>94</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>19</v>
@@ -1634,7 +1634,7 @@
         <v>88</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>19</v>
@@ -1709,7 +1709,7 @@
         <v>55</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>92</v>
@@ -1744,7 +1744,7 @@
         <v>46212</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>215</v>
@@ -1759,7 +1759,7 @@
         <v>21</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="45" x14ac:dyDescent="0.25">
@@ -1773,10 +1773,10 @@
         <v>57</v>
       </c>
       <c r="D8" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>250</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>251</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>215</v>
@@ -1791,7 +1791,7 @@
         <v>21</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="45" x14ac:dyDescent="0.25">
@@ -1823,7 +1823,7 @@
         <v>21</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
   </sheetData>
@@ -1895,7 +1895,7 @@
         <v>12</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>13</v>
@@ -1933,7 +1933,7 @@
         <v>97</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>96</v>
@@ -1971,7 +1971,7 @@
         <v>99</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>96</v>
@@ -2009,7 +2009,7 @@
         <v>99</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>96</v>
@@ -2047,7 +2047,7 @@
         <v>99</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>96</v>
@@ -2085,7 +2085,7 @@
         <v>100</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>96</v>
@@ -2123,7 +2123,7 @@
         <v>99</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>96</v>
@@ -2161,7 +2161,7 @@
         <v>101</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>96</v>
@@ -2199,7 +2199,7 @@
         <v>102</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>96</v>
@@ -2284,7 +2284,7 @@
         <v>12</v>
       </c>
       <c r="I2" s="14" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>13</v>
@@ -2322,7 +2322,7 @@
         <v>128</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>96</v>
@@ -2360,7 +2360,7 @@
         <v>128</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>96</v>
@@ -2398,7 +2398,7 @@
         <v>129</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>96</v>
@@ -2436,7 +2436,7 @@
         <v>129</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>96</v>
@@ -2474,7 +2474,7 @@
         <v>130</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>96</v>
@@ -2512,7 +2512,7 @@
         <v>102</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>96</v>
@@ -2597,7 +2597,7 @@
         <v>12</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>13</v>
@@ -2635,7 +2635,7 @@
         <v>159</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>96</v>
@@ -2673,7 +2673,7 @@
         <v>160</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>96</v>
@@ -2711,7 +2711,7 @@
         <v>159</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>96</v>
@@ -2749,7 +2749,7 @@
         <v>159</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>96</v>
@@ -2787,7 +2787,7 @@
         <v>161</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>96</v>
@@ -2825,7 +2825,7 @@
         <v>161</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>96</v>
@@ -2863,7 +2863,7 @@
         <v>128</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>96</v>
@@ -2901,7 +2901,7 @@
         <v>159</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>96</v>
@@ -2986,7 +2986,7 @@
         <v>12</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>13</v>
@@ -3024,7 +3024,7 @@
         <v>128</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>96</v>
@@ -3062,7 +3062,7 @@
         <v>71</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>96</v>
@@ -3100,7 +3100,7 @@
         <v>128</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>96</v>
@@ -3252,7 +3252,7 @@
         <v>71</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>96</v>
@@ -3290,7 +3290,7 @@
         <v>193</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>96</v>
@@ -3452,7 +3452,7 @@
         <v>12</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>13</v>
@@ -3490,7 +3490,7 @@
         <v>97</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>96</v>
@@ -3528,7 +3528,7 @@
         <v>213</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>96</v>
@@ -3560,13 +3560,13 @@
         <v>19</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H5" s="5" t="s">
         <v>213</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>96</v>
@@ -3586,7 +3586,7 @@
         <v>203</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>49</v>
@@ -3598,13 +3598,13 @@
         <v>19</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>213</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>96</v>
@@ -3636,13 +3636,13 @@
         <v>19</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>214</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
@@ -3653,10 +3653,10 @@
         <v>199</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>49</v>
@@ -3665,33 +3665,33 @@
         <v>46121</v>
       </c>
       <c r="F8" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>273</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="I8" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="J8" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="K8" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="L8" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="M8" s="6" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
         <v>219</v>
-      </c>
-      <c r="G8" s="13" t="s">
-        <v>272</v>
-      </c>
-      <c r="H8" s="12" t="s">
-        <v>223</v>
-      </c>
-      <c r="I8" s="12" t="s">
-        <v>273</v>
-      </c>
-      <c r="J8" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="K8" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="L8" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="M8" s="6" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>220</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>205</v>
@@ -3706,16 +3706,16 @@
         <v>46121</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>96</v>
+        <v>19</v>
+      </c>
+      <c r="G9" s="7">
+        <v>46062</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>102</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>96</v>
+        <v>274</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>96</v>

--- a/docs/09-Project_Plan/9-Project_Plan.xlsx
+++ b/docs/09-Project_Plan/9-Project_Plan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\College_Backup\BTech_Internship\Persistent_Project\Dataset-Pipeline\NoCodeDatasetPreprocessing\docs\09-Project_Plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71FE0C61-3DD5-42CA-8CCF-6020EB1F18F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98C453D6-7E9C-430E-9EDC-03508561142D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="317" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="2595" windowWidth="20730" windowHeight="11760" tabRatio="317" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Documents" sheetId="3" r:id="rId1"/>
@@ -111,9 +111,6 @@
   </si>
   <si>
     <t>M4</t>
-  </si>
-  <si>
-    <t>Scalability</t>
   </si>
   <si>
     <t>M5</t>
@@ -901,6 +898,9 @@
   </si>
   <si>
     <t xml:space="preserve">Researched the best flow for linear preprocessing and made sure the modules are structured like that </t>
+  </si>
+  <si>
+    <t>Scalability Features</t>
   </si>
 </sst>
 </file>
@@ -1341,16 +1341,16 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>61</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
@@ -1358,16 +1358,16 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>64</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>19</v>
@@ -1375,16 +1375,16 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>67</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>19</v>
@@ -1392,16 +1392,16 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>69</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>70</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>19</v>
@@ -1409,16 +1409,16 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>72</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>19</v>
@@ -1426,16 +1426,16 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>73</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>74</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>19</v>
@@ -1443,16 +1443,16 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>76</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>77</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>19</v>
@@ -1460,53 +1460,53 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>79</v>
-      </c>
       <c r="D8" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>229</v>
-      </c>
       <c r="D9" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>231</v>
-      </c>
       <c r="D10" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -1573,7 +1573,7 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -1582,7 +1582,7 @@
         <v>5</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -1590,22 +1590,22 @@
         <v>17</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>19</v>
@@ -1619,22 +1619,22 @@
         <v>18</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>19</v>
@@ -1648,22 +1648,22 @@
         <v>20</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>19</v>
@@ -1677,54 +1677,54 @@
         <v>22</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="F5" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>19</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E6" s="7">
         <v>46121</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G6" s="7">
         <v>46121</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>21</v>
@@ -1732,25 +1732,25 @@
     </row>
     <row r="7" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>23</v>
+        <v>274</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D7" s="7">
         <v>46212</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>21</v>
@@ -1759,30 +1759,30 @@
         <v>21</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B8" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>57</v>
-      </c>
       <c r="D8" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>250</v>
-      </c>
       <c r="F8" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>21</v>
@@ -1791,39 +1791,39 @@
         <v>21</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="C9" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="H9" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>32</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>21</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
   </sheetData>
@@ -1855,7 +1855,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -1895,7 +1895,7 @@
         <v>12</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>13</v>
@@ -1909,306 +1909,306 @@
     </row>
     <row r="3" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G4" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="H4" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="H4" s="5" t="s">
-        <v>99</v>
-      </c>
       <c r="I4" s="5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G5" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="H5" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="H5" s="5" t="s">
-        <v>99</v>
-      </c>
       <c r="I5" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G6" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="H6" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="H6" s="5" t="s">
-        <v>99</v>
-      </c>
       <c r="I6" s="5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -2244,7 +2244,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -2284,7 +2284,7 @@
         <v>12</v>
       </c>
       <c r="I2" s="14" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>13</v>
@@ -2298,230 +2298,230 @@
     </row>
     <row r="3" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -2557,7 +2557,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -2597,7 +2597,7 @@
         <v>12</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>13</v>
@@ -2611,16 +2611,16 @@
     </row>
     <row r="3" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E3" s="7">
         <v>46089</v>
@@ -2632,33 +2632,33 @@
         <v>46089</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E4" s="7">
         <v>46120</v>
@@ -2670,33 +2670,33 @@
         <v>46120</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E5" s="7">
         <v>46120</v>
@@ -2708,33 +2708,33 @@
         <v>46120</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E6" s="7">
         <v>46181</v>
@@ -2746,33 +2746,33 @@
         <v>46120</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E7" s="7">
         <v>46181</v>
@@ -2784,133 +2784,133 @@
         <v>46120</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B8" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>158</v>
-      </c>
       <c r="D8" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E8" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>150</v>
-      </c>
       <c r="H8" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C9" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E9" s="3" t="s">
+      <c r="F9" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>150</v>
-      </c>
       <c r="H9" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="C10" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>156</v>
-      </c>
       <c r="D10" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E10" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>150</v>
-      </c>
       <c r="H10" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -2946,7 +2946,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -2986,7 +2986,7 @@
         <v>12</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>13</v>
@@ -3000,382 +3000,382 @@
     </row>
     <row r="3" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -3412,7 +3412,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -3452,7 +3452,7 @@
         <v>12</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>13</v>
@@ -3466,168 +3466,168 @@
     </row>
     <row r="3" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E4" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H4" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>213</v>
-      </c>
       <c r="I4" s="5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E7" s="7">
         <v>46031</v>
@@ -3636,13 +3636,13 @@
         <v>19</v>
       </c>
       <c r="G7" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="I7" s="5" t="s">
         <v>269</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>270</v>
       </c>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
@@ -3650,16 +3650,16 @@
     </row>
     <row r="8" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E8" s="13">
         <v>46121</v>
@@ -3668,39 +3668,39 @@
         <v>19</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H8" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="I8" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="J8" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="K8" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="L8" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="M8" s="6" t="s">
         <v>222</v>
-      </c>
-      <c r="I8" s="12" t="s">
-        <v>271</v>
-      </c>
-      <c r="J8" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="K8" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="L8" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="M8" s="6" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E9" s="7">
         <v>46121</v>
@@ -3712,19 +3712,19 @@
         <v>46062</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/docs/09-Project_Plan/9-Project_Plan.xlsx
+++ b/docs/09-Project_Plan/9-Project_Plan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\College_Backup\BTech_Internship\Persistent_Project\Dataset-Pipeline\NoCodeDatasetPreprocessing\docs\09-Project_Plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98C453D6-7E9C-430E-9EDC-03508561142D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0840311E-6AA0-4435-BBCA-96FA5455825E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="2595" windowWidth="20730" windowHeight="11760" tabRatio="317" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="317" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Documents" sheetId="3" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="275">
   <si>
     <t>Milestone Name</t>
   </si>
@@ -852,9 +852,6 @@
   </si>
   <si>
     <t>Researching how heatmaps can be displayed properly on streamlit. Trial and error about how to render the image</t>
-  </si>
-  <si>
-    <t>Added an extra section, which I later got to know, I should not be doing as this expands the scope, should have added this in the initial draft itself. Implemented basic info,pcc,null count</t>
   </si>
   <si>
     <r>
@@ -894,13 +891,16 @@
     </r>
   </si>
   <si>
-    <t>01/09/2026 (major)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Researched the best flow for linear preprocessing and made sure the modules are structured like that </t>
   </si>
   <si>
     <t>Scalability Features</t>
+  </si>
+  <si>
+    <t>04/09/2026 (major)</t>
+  </si>
+  <si>
+    <t>Added an extra section, which I later got to know, I should not be doing as this expands the scope, should have added this in the initial draft itself. Implemented basic info,pcc,null count. Added 2 sections (describe and value counts) they took lot of logical working</t>
   </si>
 </sst>
 </file>
@@ -1717,8 +1717,8 @@
       <c r="E6" s="7">
         <v>46121</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>95</v>
+      <c r="F6" s="10">
+        <v>46121</v>
       </c>
       <c r="G6" s="7">
         <v>46121</v>
@@ -1735,7 +1735,7 @@
         <v>24</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>52</v>
@@ -1791,7 +1791,7 @@
         <v>21</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="45" x14ac:dyDescent="0.25">
@@ -3648,7 +3648,7 @@
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
     </row>
-    <row r="8" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>198</v>
       </c>
@@ -3668,13 +3668,13 @@
         <v>19</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H8" s="12" t="s">
         <v>221</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="J8" s="11" t="s">
         <v>95</v>
@@ -3715,7 +3715,7 @@
         <v>101</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>95</v>
